--- a/artfynd/A 52496-2025 artfynd.xlsx
+++ b/artfynd/A 52496-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY100"/>
+  <dimension ref="A1:AY101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12215,6 +12215,111 @@
         </is>
       </c>
     </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>129805600</v>
+      </c>
+      <c r="B101" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Risåsen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>407736</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6969699</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 52496-2025 artfynd.xlsx
+++ b/artfynd/A 52496-2025 artfynd.xlsx
@@ -12220,7 +12220,7 @@
         <v>129805600</v>
       </c>
       <c r="B101" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>

--- a/artfynd/A 52496-2025 artfynd.xlsx
+++ b/artfynd/A 52496-2025 artfynd.xlsx
@@ -12220,7 +12220,7 @@
         <v>129805600</v>
       </c>
       <c r="B101" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>

--- a/artfynd/A 52496-2025 artfynd.xlsx
+++ b/artfynd/A 52496-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY151"/>
+  <dimension ref="A1:AZ151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79078249</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79078250</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79078352</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79078410</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79082485</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1283,6 +1313,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79094581</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1394,6 +1429,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79115898</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1495,6 +1535,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79082456</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1596,6 +1641,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79078409</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1697,6 +1747,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79082487</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1798,6 +1853,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79078342</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1909,6 +1969,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79095783</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2020,6 +2085,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79095784</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2131,6 +2201,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79095785</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2235,6 +2310,11 @@
       <c r="AY16" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79078264</t>
         </is>
       </c>
     </row>
@@ -2342,6 +2422,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79082448</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2443,6 +2528,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79078260</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2544,6 +2634,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79082481</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2645,6 +2740,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79078372</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2746,6 +2846,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79082463</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2847,6 +2952,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79082464</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2958,6 +3068,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79095775</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3069,6 +3184,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79095776</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3170,6 +3290,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79078257</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3271,6 +3396,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79078288</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3372,6 +3502,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79078359</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3473,6 +3608,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79078360</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3574,6 +3714,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79078361</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3675,6 +3820,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79082479</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3776,6 +3926,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79082482</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3877,6 +4032,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79078376</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3978,6 +4138,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79078377</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4089,6 +4254,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79095781</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4190,6 +4360,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79078261</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4291,6 +4466,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79078305</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4402,6 +4582,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79115906</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4503,6 +4688,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79078266</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4604,6 +4794,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79078382</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4705,6 +4900,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79082457</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4806,6 +5006,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79094589</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4917,6 +5122,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79115913</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5028,6 +5238,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79115914</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5139,6 +5354,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79115915</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5254,6 +5474,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113178421</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5369,6 +5594,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113178422</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5484,6 +5714,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113178424</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5585,6 +5820,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79078314</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5686,6 +5926,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79094577</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5797,6 +6042,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79115910</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5899,6 +6149,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79078309</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6010,6 +6265,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79115896</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6125,6 +6385,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113178448</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6240,6 +6505,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113178449</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6355,6 +6625,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113178450</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6470,6 +6745,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113178445</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6571,6 +6851,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79078354</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6672,6 +6957,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79078333</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6773,6 +7063,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79078393</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6874,6 +7169,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79078396</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6975,6 +7275,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79078398</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7076,6 +7381,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79078408</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7177,6 +7487,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79078426</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7278,6 +7593,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79082441</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7379,6 +7699,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79082449</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7480,6 +7805,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79082461</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7586,6 +7916,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79094586</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7692,6 +8027,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79094587</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7798,6 +8138,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79094588</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7909,6 +8254,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79095780</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8020,6 +8370,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79115916</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8121,6 +8476,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79078406</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8222,6 +8582,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79082458</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8333,6 +8698,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79095790</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8434,6 +8804,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79078324</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8535,6 +8910,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79078325</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8637,6 +9017,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79078247</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8738,6 +9123,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79078276</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8839,6 +9229,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79078278</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8940,6 +9335,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79078279</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9041,6 +9441,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79078349</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9142,6 +9547,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79078350</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9243,6 +9653,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79082440</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9344,6 +9759,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79082442</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9445,6 +9865,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79082452</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9546,6 +9971,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79082459</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9652,6 +10082,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79094578</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9763,6 +10198,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79095761</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9874,6 +10314,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79095774</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9976,6 +10421,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79078253</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10078,6 +10528,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79078357</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10179,6 +10634,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79082443</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10280,6 +10740,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79082447</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10391,6 +10856,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79095762</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10502,6 +10972,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79095763</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10613,6 +11088,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79095764</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10724,6 +11204,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79115899</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10835,6 +11320,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79115900</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10936,6 +11426,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79078311</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11037,6 +11532,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79082484</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11142,6 +11642,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129805600</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11258,6 +11763,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79092762</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11359,6 +11869,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79078363</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11460,6 +11975,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79078370</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11561,6 +12081,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79094583</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11672,6 +12197,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79095773</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11773,6 +12303,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79094579</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11884,6 +12419,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79095837</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11985,6 +12525,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79078420</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12096,6 +12641,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79095786</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12197,6 +12747,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79078316</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12298,6 +12853,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79078317</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12399,6 +12959,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79078423</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12500,6 +13065,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79078246</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12601,6 +13171,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79078273</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12702,6 +13277,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79078344</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12803,6 +13383,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79078346</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12904,6 +13489,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79094582</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13005,6 +13595,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79094584</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13116,6 +13711,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79095754</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13227,6 +13827,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79095755</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13338,6 +13943,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79115895</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13439,6 +14049,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79078263</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13550,6 +14165,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79115907</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13651,6 +14271,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79078308</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13752,6 +14377,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79078294</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13853,6 +14483,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79078295</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13954,6 +14589,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79078296</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -14055,6 +14695,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79078297</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14157,6 +14802,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79078364</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14258,6 +14908,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79078365</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14359,6 +15014,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79078366</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14460,6 +15120,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79078415</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14561,6 +15226,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79082438</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14662,6 +15332,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79094590</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14773,6 +15448,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79095768</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14884,6 +15564,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79095770</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14995,6 +15680,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79095771</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -15106,6 +15796,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79115904</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -15217,6 +15912,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79115905</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -15318,6 +16018,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79078286</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -15417,6 +16122,11 @@
       <c r="AY142" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
+        </is>
+      </c>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79078290</t>
         </is>
       </c>
     </row>
@@ -15529,6 +16239,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79078341</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -15640,6 +16355,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79115909</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -15741,6 +16461,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79078323</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -15842,6 +16567,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79082483</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -15953,6 +16683,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79095765</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -16064,6 +16799,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79115902</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -16165,6 +16905,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79078291</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -16266,6 +17011,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79078292</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -16377,8 +17127,165 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79095767</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 52496-2025 artfynd.xlsx
+++ b/artfynd/A 52496-2025 artfynd.xlsx
@@ -3399,7 +3399,7 @@
         <v>135784602</v>
       </c>
       <c r="B27" t="n">
-        <v>92763</v>
+        <v>92765</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>135784603</v>
       </c>
       <c r="B37" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
         <v>135784610</v>
       </c>
       <c r="B38" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         <v>135784600</v>
       </c>
       <c r="B58" t="n">
-        <v>91970</v>
+        <v>91972</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7128,7 +7128,7 @@
         <v>135784598</v>
       </c>
       <c r="B61" t="n">
-        <v>89290</v>
+        <v>89292</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>135784604</v>
       </c>
       <c r="B65" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -15604,7 +15604,7 @@
         <v>135784613</v>
       </c>
       <c r="B139" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17453,7 +17453,7 @@
         <v>135784599</v>
       </c>
       <c r="B156" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>

--- a/artfynd/A 52496-2025 artfynd.xlsx
+++ b/artfynd/A 52496-2025 artfynd.xlsx
@@ -1758,7 +1758,7 @@
         <v>135784597</v>
       </c>
       <c r="B12" t="n">
-        <v>79473</v>
+        <v>79475</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>135784601</v>
       </c>
       <c r="B17" t="n">
-        <v>83420</v>
+        <v>83422</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>135784602</v>
       </c>
       <c r="B27" t="n">
-        <v>92765</v>
+        <v>92780</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>135784603</v>
       </c>
       <c r="B37" t="n">
-        <v>92064</v>
+        <v>92078</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
         <v>135784610</v>
       </c>
       <c r="B38" t="n">
-        <v>92064</v>
+        <v>92078</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         <v>135784600</v>
       </c>
       <c r="B58" t="n">
-        <v>91972</v>
+        <v>91986</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7128,7 +7128,7 @@
         <v>135784598</v>
       </c>
       <c r="B61" t="n">
-        <v>89292</v>
+        <v>89294</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>135784604</v>
       </c>
       <c r="B65" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         <v>135784608</v>
       </c>
       <c r="B80" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -11127,7 +11127,7 @@
         <v>135784607</v>
       </c>
       <c r="B98" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12351,7 +12351,7 @@
         <v>135784611</v>
       </c>
       <c r="B109" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12559,7 +12559,7 @@
         <v>135784605</v>
       </c>
       <c r="B111" t="n">
-        <v>80561</v>
+        <v>80563</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13104,7 +13104,7 @@
         <v>135784612</v>
       </c>
       <c r="B116" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13534,7 +13534,7 @@
         <v>135784606</v>
       </c>
       <c r="B120" t="n">
-        <v>5201</v>
+        <v>5202</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15604,7 +15604,7 @@
         <v>135784613</v>
       </c>
       <c r="B139" t="n">
-        <v>98144</v>
+        <v>98161</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17453,7 +17453,7 @@
         <v>135784599</v>
       </c>
       <c r="B156" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18442,7 +18442,7 @@
         <v>135784615</v>
       </c>
       <c r="B165" t="n">
-        <v>80031</v>
+        <v>80033</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>

--- a/artfynd/A 52496-2025 artfynd.xlsx
+++ b/artfynd/A 52496-2025 artfynd.xlsx
@@ -1758,7 +1758,7 @@
         <v>135784597</v>
       </c>
       <c r="B12" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>135784601</v>
       </c>
       <c r="B17" t="n">
-        <v>83422</v>
+        <v>83423</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>135784602</v>
       </c>
       <c r="B27" t="n">
-        <v>92780</v>
+        <v>92781</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>135784603</v>
       </c>
       <c r="B37" t="n">
-        <v>92078</v>
+        <v>92079</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
         <v>135784610</v>
       </c>
       <c r="B38" t="n">
-        <v>92078</v>
+        <v>92079</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         <v>135784600</v>
       </c>
       <c r="B58" t="n">
-        <v>91986</v>
+        <v>91987</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7128,7 +7128,7 @@
         <v>135784598</v>
       </c>
       <c r="B61" t="n">
-        <v>89294</v>
+        <v>89295</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>135784604</v>
       </c>
       <c r="B65" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         <v>135784608</v>
       </c>
       <c r="B80" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -11127,7 +11127,7 @@
         <v>135784607</v>
       </c>
       <c r="B98" t="n">
-        <v>83430</v>
+        <v>83431</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12351,7 +12351,7 @@
         <v>135784611</v>
       </c>
       <c r="B109" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12559,7 +12559,7 @@
         <v>135784605</v>
       </c>
       <c r="B111" t="n">
-        <v>80563</v>
+        <v>80564</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -15604,7 +15604,7 @@
         <v>135784613</v>
       </c>
       <c r="B139" t="n">
-        <v>98161</v>
+        <v>98162</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17453,7 +17453,7 @@
         <v>135784599</v>
       </c>
       <c r="B156" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18442,7 +18442,7 @@
         <v>135784615</v>
       </c>
       <c r="B165" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>

--- a/artfynd/A 52496-2025 artfynd.xlsx
+++ b/artfynd/A 52496-2025 artfynd.xlsx
@@ -3399,7 +3399,7 @@
         <v>135784602</v>
       </c>
       <c r="B27" t="n">
-        <v>92781</v>
+        <v>92782</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>135784603</v>
       </c>
       <c r="B37" t="n">
-        <v>92079</v>
+        <v>92080</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
         <v>135784610</v>
       </c>
       <c r="B38" t="n">
-        <v>92079</v>
+        <v>92080</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         <v>135784600</v>
       </c>
       <c r="B58" t="n">
-        <v>91987</v>
+        <v>91988</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7128,7 +7128,7 @@
         <v>135784598</v>
       </c>
       <c r="B61" t="n">
-        <v>89295</v>
+        <v>89296</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>135784604</v>
       </c>
       <c r="B65" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -15604,7 +15604,7 @@
         <v>135784613</v>
       </c>
       <c r="B139" t="n">
-        <v>98162</v>
+        <v>98163</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17453,7 +17453,7 @@
         <v>135784599</v>
       </c>
       <c r="B156" t="n">
-        <v>99316</v>
+        <v>99317</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>

--- a/artfynd/A 52496-2025 artfynd.xlsx
+++ b/artfynd/A 52496-2025 artfynd.xlsx
@@ -1758,7 +1758,7 @@
         <v>135784597</v>
       </c>
       <c r="B12" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>135784601</v>
       </c>
       <c r="B17" t="n">
-        <v>83423</v>
+        <v>83424</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>135784602</v>
       </c>
       <c r="B27" t="n">
-        <v>92782</v>
+        <v>92783</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>135784603</v>
       </c>
       <c r="B37" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
         <v>135784610</v>
       </c>
       <c r="B38" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         <v>135784600</v>
       </c>
       <c r="B58" t="n">
-        <v>91988</v>
+        <v>91989</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7128,7 +7128,7 @@
         <v>135784598</v>
       </c>
       <c r="B61" t="n">
-        <v>89296</v>
+        <v>89297</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>135784604</v>
       </c>
       <c r="B65" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         <v>135784608</v>
       </c>
       <c r="B80" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -11127,7 +11127,7 @@
         <v>135784607</v>
       </c>
       <c r="B98" t="n">
-        <v>83431</v>
+        <v>83432</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12351,7 +12351,7 @@
         <v>135784611</v>
       </c>
       <c r="B109" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12559,7 +12559,7 @@
         <v>135784605</v>
       </c>
       <c r="B111" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13104,7 +13104,7 @@
         <v>135784612</v>
       </c>
       <c r="B116" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -15604,7 +15604,7 @@
         <v>135784613</v>
       </c>
       <c r="B139" t="n">
-        <v>98163</v>
+        <v>98164</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17453,7 +17453,7 @@
         <v>135784599</v>
       </c>
       <c r="B156" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18442,7 +18442,7 @@
         <v>135784615</v>
       </c>
       <c r="B165" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>

--- a/artfynd/A 52496-2025 artfynd.xlsx
+++ b/artfynd/A 52496-2025 artfynd.xlsx
@@ -1758,7 +1758,7 @@
         <v>135784597</v>
       </c>
       <c r="B12" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>135784601</v>
       </c>
       <c r="B17" t="n">
-        <v>83424</v>
+        <v>83428</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>135784602</v>
       </c>
       <c r="B27" t="n">
-        <v>92783</v>
+        <v>92789</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>135784603</v>
       </c>
       <c r="B37" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
         <v>135784610</v>
       </c>
       <c r="B38" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         <v>135784600</v>
       </c>
       <c r="B58" t="n">
-        <v>91989</v>
+        <v>91995</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7128,7 +7128,7 @@
         <v>135784598</v>
       </c>
       <c r="B61" t="n">
-        <v>89297</v>
+        <v>89303</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>135784604</v>
       </c>
       <c r="B65" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         <v>135784608</v>
       </c>
       <c r="B80" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -11127,7 +11127,7 @@
         <v>135784607</v>
       </c>
       <c r="B98" t="n">
-        <v>83432</v>
+        <v>83436</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12351,7 +12351,7 @@
         <v>135784611</v>
       </c>
       <c r="B109" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12559,7 +12559,7 @@
         <v>135784605</v>
       </c>
       <c r="B111" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13104,7 +13104,7 @@
         <v>135784612</v>
       </c>
       <c r="B116" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -15604,7 +15604,7 @@
         <v>135784613</v>
       </c>
       <c r="B139" t="n">
-        <v>98164</v>
+        <v>98170</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17453,7 +17453,7 @@
         <v>135784599</v>
       </c>
       <c r="B156" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18442,7 +18442,7 @@
         <v>135784615</v>
       </c>
       <c r="B165" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>

--- a/artfynd/A 52496-2025 artfynd.xlsx
+++ b/artfynd/A 52496-2025 artfynd.xlsx
@@ -1758,7 +1758,7 @@
         <v>135784597</v>
       </c>
       <c r="B12" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>135784601</v>
       </c>
       <c r="B17" t="n">
-        <v>83428</v>
+        <v>83429</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>135784602</v>
       </c>
       <c r="B27" t="n">
-        <v>92789</v>
+        <v>92790</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>135784603</v>
       </c>
       <c r="B37" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
         <v>135784610</v>
       </c>
       <c r="B38" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         <v>135784600</v>
       </c>
       <c r="B58" t="n">
-        <v>91995</v>
+        <v>91996</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7128,7 +7128,7 @@
         <v>135784598</v>
       </c>
       <c r="B61" t="n">
-        <v>89303</v>
+        <v>89304</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>135784604</v>
       </c>
       <c r="B65" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         <v>135784608</v>
       </c>
       <c r="B80" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -11127,7 +11127,7 @@
         <v>135784607</v>
       </c>
       <c r="B98" t="n">
-        <v>83436</v>
+        <v>83437</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12351,7 +12351,7 @@
         <v>135784611</v>
       </c>
       <c r="B109" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12559,7 +12559,7 @@
         <v>135784605</v>
       </c>
       <c r="B111" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13104,7 +13104,7 @@
         <v>135784612</v>
       </c>
       <c r="B116" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -15604,7 +15604,7 @@
         <v>135784613</v>
       </c>
       <c r="B139" t="n">
-        <v>98170</v>
+        <v>98171</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17453,7 +17453,7 @@
         <v>135784599</v>
       </c>
       <c r="B156" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18442,7 +18442,7 @@
         <v>135784615</v>
       </c>
       <c r="B165" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>

--- a/artfynd/A 52496-2025 artfynd.xlsx
+++ b/artfynd/A 52496-2025 artfynd.xlsx
@@ -1758,7 +1758,7 @@
         <v>135784597</v>
       </c>
       <c r="B12" t="n">
-        <v>79482</v>
+        <v>79486</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>135784601</v>
       </c>
       <c r="B17" t="n">
-        <v>83429</v>
+        <v>83433</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>135784602</v>
       </c>
       <c r="B27" t="n">
-        <v>92790</v>
+        <v>92796</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>135784603</v>
       </c>
       <c r="B37" t="n">
-        <v>92088</v>
+        <v>92094</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
         <v>135784610</v>
       </c>
       <c r="B38" t="n">
-        <v>92088</v>
+        <v>92094</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         <v>135784600</v>
       </c>
       <c r="B58" t="n">
-        <v>91996</v>
+        <v>92002</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7128,7 +7128,7 @@
         <v>135784598</v>
       </c>
       <c r="B61" t="n">
-        <v>89304</v>
+        <v>89310</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>135784604</v>
       </c>
       <c r="B65" t="n">
-        <v>92037</v>
+        <v>92043</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         <v>135784608</v>
       </c>
       <c r="B80" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -11127,7 +11127,7 @@
         <v>135784607</v>
       </c>
       <c r="B98" t="n">
-        <v>83437</v>
+        <v>83441</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12351,7 +12351,7 @@
         <v>135784611</v>
       </c>
       <c r="B109" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12559,7 +12559,7 @@
         <v>135784605</v>
       </c>
       <c r="B111" t="n">
-        <v>80570</v>
+        <v>80574</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -15604,7 +15604,7 @@
         <v>135784613</v>
       </c>
       <c r="B139" t="n">
-        <v>98171</v>
+        <v>98182</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17453,7 +17453,7 @@
         <v>135784599</v>
       </c>
       <c r="B156" t="n">
-        <v>99325</v>
+        <v>99336</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18442,7 +18442,7 @@
         <v>135784615</v>
       </c>
       <c r="B165" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>

--- a/artfynd/A 52496-2025 artfynd.xlsx
+++ b/artfynd/A 52496-2025 artfynd.xlsx
@@ -1758,7 +1758,7 @@
         <v>135784597</v>
       </c>
       <c r="B12" t="n">
-        <v>79486</v>
+        <v>79492</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>135784601</v>
       </c>
       <c r="B17" t="n">
-        <v>83433</v>
+        <v>83439</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>135784602</v>
       </c>
       <c r="B27" t="n">
-        <v>92796</v>
+        <v>92803</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>135784603</v>
       </c>
       <c r="B37" t="n">
-        <v>92094</v>
+        <v>92101</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
         <v>135784610</v>
       </c>
       <c r="B38" t="n">
-        <v>92094</v>
+        <v>92101</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         <v>135784600</v>
       </c>
       <c r="B58" t="n">
-        <v>92002</v>
+        <v>92009</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7128,7 +7128,7 @@
         <v>135784598</v>
       </c>
       <c r="B61" t="n">
-        <v>89310</v>
+        <v>89317</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>135784604</v>
       </c>
       <c r="B65" t="n">
-        <v>92043</v>
+        <v>92050</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         <v>135784608</v>
       </c>
       <c r="B80" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -11127,7 +11127,7 @@
         <v>135784607</v>
       </c>
       <c r="B98" t="n">
-        <v>83441</v>
+        <v>83447</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12351,7 +12351,7 @@
         <v>135784611</v>
       </c>
       <c r="B109" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12559,7 +12559,7 @@
         <v>135784605</v>
       </c>
       <c r="B111" t="n">
-        <v>80574</v>
+        <v>80580</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13104,7 +13104,7 @@
         <v>135784612</v>
       </c>
       <c r="B116" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -15604,7 +15604,7 @@
         <v>135784613</v>
       </c>
       <c r="B139" t="n">
-        <v>98182</v>
+        <v>98195</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17453,7 +17453,7 @@
         <v>135784599</v>
       </c>
       <c r="B156" t="n">
-        <v>99336</v>
+        <v>99349</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18442,7 +18442,7 @@
         <v>135784615</v>
       </c>
       <c r="B165" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>

--- a/artfynd/A 52496-2025 artfynd.xlsx
+++ b/artfynd/A 52496-2025 artfynd.xlsx
@@ -3399,7 +3399,7 @@
         <v>135784602</v>
       </c>
       <c r="B27" t="n">
-        <v>92803</v>
+        <v>92804</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>135784603</v>
       </c>
       <c r="B37" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
         <v>135784610</v>
       </c>
       <c r="B38" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         <v>135784600</v>
       </c>
       <c r="B58" t="n">
-        <v>92009</v>
+        <v>92010</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7128,7 +7128,7 @@
         <v>135784598</v>
       </c>
       <c r="B61" t="n">
-        <v>89317</v>
+        <v>89318</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>135784604</v>
       </c>
       <c r="B65" t="n">
-        <v>92050</v>
+        <v>92051</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -15604,7 +15604,7 @@
         <v>135784613</v>
       </c>
       <c r="B139" t="n">
-        <v>98195</v>
+        <v>98196</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -17453,7 +17453,7 @@
         <v>135784599</v>
       </c>
       <c r="B156" t="n">
-        <v>99349</v>
+        <v>99350</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
